--- a/data/question_master.xlsx
+++ b/data/question_master.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\km78617\Documents\GitHub\kikai-gakka-exam\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED02B152-B843-4CCB-AA67-AAC028811114}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FB7D1B3-C7A0-4357-8CBD-037A6992791C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6406" uniqueCount="3629">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6411" uniqueCount="3634">
   <si>
     <t>id</t>
   </si>
@@ -13107,6 +13107,67 @@
     <t>品質管理</t>
     <phoneticPr fontId="4"/>
   </si>
+  <si>
+    <t>選択肢修正</t>
+    <rPh sb="0" eb="5">
+      <t>センタクシシュウセイ</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="6"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>１：２</t>
+    </r>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="6"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>１：５</t>
+    </r>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <r>
+      <t>２</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="6"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>：１</t>
+    </r>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <r>
+      <t>３</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="6"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>：１</t>
+    </r>
+    <phoneticPr fontId="4"/>
+  </si>
 </sst>
 </file>
 
@@ -13206,7 +13267,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -13234,6 +13295,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -13248,7 +13315,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -13293,6 +13360,18 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="6" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="6" fillId="6" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -44344,7 +44423,7 @@
         <v>46210</v>
       </c>
     </row>
-    <row r="673" spans="1:26" ht="25.2">
+    <row r="673" spans="1:27" ht="25.2">
       <c r="A673" s="9" t="s">
         <v>3306</v>
       </c>
@@ -44406,7 +44485,7 @@
         <v>46210</v>
       </c>
     </row>
-    <row r="674" spans="1:26" ht="25.2">
+    <row r="674" spans="1:27" ht="25.2">
       <c r="A674" s="10" t="s">
         <v>3316</v>
       </c>
@@ -44464,7 +44543,7 @@
         <v>46210</v>
       </c>
     </row>
-    <row r="675" spans="1:26" ht="25.2">
+    <row r="675" spans="1:27" ht="25.2">
       <c r="A675" s="9" t="s">
         <v>3322</v>
       </c>
@@ -44529,7 +44608,7 @@
         <v>46210</v>
       </c>
     </row>
-    <row r="676" spans="1:26" ht="25.2">
+    <row r="676" spans="1:27" ht="25.2">
       <c r="A676" s="9" t="s">
         <v>3328</v>
       </c>
@@ -44594,7 +44673,7 @@
         <v>46210</v>
       </c>
     </row>
-    <row r="677" spans="1:26" ht="25.2">
+    <row r="677" spans="1:27" ht="25.2">
       <c r="A677" s="9" t="s">
         <v>3334</v>
       </c>
@@ -44656,69 +44735,78 @@
         <v>46210</v>
       </c>
     </row>
-    <row r="678" spans="1:26" ht="25.2">
-      <c r="A678" s="9" t="s">
+    <row r="678" spans="1:27" ht="25.2">
+      <c r="A678" s="16" t="s">
         <v>3344</v>
       </c>
-      <c r="B678" s="9" t="s">
+      <c r="B678" s="16" t="s">
         <v>151</v>
       </c>
-      <c r="C678" s="9">
+      <c r="C678" s="16">
         <v>157</v>
       </c>
-      <c r="D678" s="9" t="s">
+      <c r="D678" s="16" t="s">
         <v>25</v>
       </c>
-      <c r="E678" s="9" t="s">
+      <c r="E678" s="16" t="s">
         <v>219</v>
       </c>
-      <c r="H678" s="9" t="s">
+      <c r="F678" s="16"/>
+      <c r="G678" s="16"/>
+      <c r="H678" s="16" t="s">
         <v>3345</v>
       </c>
-      <c r="J678" s="9">
-        <v>4.3055555555555555E-2</v>
-      </c>
-      <c r="K678" s="9">
-        <v>4.5138888888888888E-2</v>
-      </c>
-      <c r="L678" s="9">
-        <v>8.4027777777777785E-2</v>
-      </c>
-      <c r="M678" s="9">
-        <v>0.12569444444444444</v>
-      </c>
-      <c r="N678" s="9" t="s">
+      <c r="I678" s="16"/>
+      <c r="J678" s="18" t="s">
+        <v>3630</v>
+      </c>
+      <c r="K678" s="19" t="s">
+        <v>3631</v>
+      </c>
+      <c r="L678" s="19" t="s">
+        <v>3632</v>
+      </c>
+      <c r="M678" s="19" t="s">
+        <v>3633</v>
+      </c>
+      <c r="N678" s="16" t="s">
         <v>3346</v>
       </c>
-      <c r="O678" s="9" t="s">
+      <c r="O678" s="16" t="s">
         <v>3347</v>
       </c>
-      <c r="P678" s="9" t="s">
+      <c r="P678" s="16" t="s">
         <v>3348</v>
       </c>
-      <c r="Q678" s="9" t="s">
+      <c r="Q678" s="16" t="s">
         <v>3349</v>
       </c>
-      <c r="R678" s="9" t="s">
+      <c r="R678" s="16" t="s">
         <v>43</v>
       </c>
-      <c r="U678" s="9" t="b">
-        <v>1</v>
-      </c>
-      <c r="W678" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="X678" s="9" t="b">
-        <v>1</v>
-      </c>
-      <c r="Y678" s="9">
-        <v>1</v>
-      </c>
-      <c r="Z678" s="6">
-        <v>46210</v>
-      </c>
-    </row>
-    <row r="679" spans="1:26" ht="25.2">
+      <c r="S678" s="16"/>
+      <c r="T678" s="16"/>
+      <c r="U678" s="16" t="b">
+        <v>1</v>
+      </c>
+      <c r="V678" s="16"/>
+      <c r="W678" s="16" t="b">
+        <v>0</v>
+      </c>
+      <c r="X678" s="16" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y678" s="16">
+        <v>1</v>
+      </c>
+      <c r="Z678" s="17">
+        <v>46289</v>
+      </c>
+      <c r="AA678" s="16" t="s">
+        <v>3629</v>
+      </c>
+    </row>
+    <row r="679" spans="1:27" ht="25.2">
       <c r="A679" s="9" t="s">
         <v>3350</v>
       </c>
@@ -44780,7 +44868,7 @@
         <v>46210</v>
       </c>
     </row>
-    <row r="680" spans="1:26" ht="25.2">
+    <row r="680" spans="1:27" ht="25.2">
       <c r="A680" s="9" t="s">
         <v>3360</v>
       </c>
@@ -44842,7 +44930,7 @@
         <v>46210</v>
       </c>
     </row>
-    <row r="681" spans="1:26" ht="25.2">
+    <row r="681" spans="1:27" ht="25.2">
       <c r="A681" s="9" t="s">
         <v>3368</v>
       </c>
@@ -44904,7 +44992,7 @@
         <v>46210</v>
       </c>
     </row>
-    <row r="682" spans="1:26" ht="25.2">
+    <row r="682" spans="1:27" ht="25.2">
       <c r="A682" s="9" t="s">
         <v>3378</v>
       </c>
@@ -44957,7 +45045,7 @@
         <v>46210</v>
       </c>
     </row>
-    <row r="683" spans="1:26" ht="25.2">
+    <row r="683" spans="1:27" ht="25.2">
       <c r="A683" s="9" t="s">
         <v>3380</v>
       </c>
@@ -45019,7 +45107,7 @@
         <v>46210</v>
       </c>
     </row>
-    <row r="684" spans="1:26" ht="25.2">
+    <row r="684" spans="1:27" ht="25.2">
       <c r="A684" s="9" t="s">
         <v>3390</v>
       </c>
@@ -45081,7 +45169,7 @@
         <v>46210</v>
       </c>
     </row>
-    <row r="685" spans="1:26" ht="25.2">
+    <row r="685" spans="1:27" ht="25.2">
       <c r="A685" s="9" t="s">
         <v>3400</v>
       </c>
@@ -45146,7 +45234,7 @@
         <v>46210</v>
       </c>
     </row>
-    <row r="686" spans="1:26" ht="25.2">
+    <row r="686" spans="1:27" ht="25.2">
       <c r="A686" s="9" t="s">
         <v>3406</v>
       </c>
@@ -45208,7 +45296,7 @@
         <v>46210</v>
       </c>
     </row>
-    <row r="687" spans="1:26" ht="25.2">
+    <row r="687" spans="1:27" ht="25.2">
       <c r="A687" s="9" t="s">
         <v>3412</v>
       </c>
@@ -45270,7 +45358,7 @@
         <v>46210</v>
       </c>
     </row>
-    <row r="688" spans="1:26" ht="25.2">
+    <row r="688" spans="1:27" ht="25.2">
       <c r="A688" s="9" t="s">
         <v>3422</v>
       </c>
